--- a/缓存数据/concat_area_csm_xm.xlsx
+++ b/缓存数据/concat_area_csm_xm.xlsx
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2881224.11</v>
+        <v>2034261.629999999</v>
       </c>
       <c r="C2" t="n">
-        <v>708992.6699999989</v>
+        <v>729884.9899999998</v>
       </c>
       <c r="D2" t="n">
-        <v>583939.2499999993</v>
+        <v>577543.75</v>
       </c>
       <c r="E2" t="n">
-        <v>125053.42</v>
+        <v>152341.24</v>
       </c>
       <c r="F2" t="n">
-        <v>421430.79</v>
+        <v>439059.9699999999</v>
       </c>
       <c r="G2" t="n">
-        <v>287561.8800000003</v>
+        <v>290825.02</v>
       </c>
       <c r="H2" t="n">
-        <v>16158.03</v>
+        <v>16151.93</v>
       </c>
       <c r="I2" t="n">
-        <v>1301231.44</v>
+        <v>1304376.639999999</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2034261.629999998</v>
+        <v>2022394.340000002</v>
       </c>
       <c r="C3" t="n">
-        <v>729884.9899999993</v>
+        <v>728751.3399999997</v>
       </c>
       <c r="D3" t="n">
-        <v>577543.75</v>
+        <v>563337.62</v>
       </c>
       <c r="E3" t="n">
-        <v>152341.24</v>
+        <v>165413.7200000001</v>
       </c>
       <c r="F3" t="n">
-        <v>439059.97</v>
+        <v>445433.47</v>
       </c>
       <c r="G3" t="n">
-        <v>290825.0200000001</v>
+        <v>283317.8699999998</v>
       </c>
       <c r="H3" t="n">
-        <v>16151.93</v>
+        <v>16225.19</v>
       </c>
       <c r="I3" t="n">
-        <v>1304376.639999999</v>
+        <v>1293643.000000002</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2022394.340000002</v>
+        <v>1994908.029999998</v>
       </c>
       <c r="C4" t="n">
-        <v>728751.3399999996</v>
+        <v>683861.439999999</v>
       </c>
       <c r="D4" t="n">
-        <v>563337.6199999999</v>
+        <v>512271.8200000006</v>
       </c>
       <c r="E4" t="n">
-        <v>165413.7200000001</v>
+        <v>171589.62</v>
       </c>
       <c r="F4" t="n">
-        <v>445433.47</v>
+        <v>449865.2500000002</v>
       </c>
       <c r="G4" t="n">
-        <v>283317.8699999998</v>
+        <v>233996.1899999999</v>
       </c>
       <c r="H4" t="n">
-        <v>16225.19</v>
+        <v>15780.09</v>
       </c>
       <c r="I4" t="n">
-        <v>1293643.000000002</v>
+        <v>1311046.589999999</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1994908.03</v>
+        <v>1945284.92</v>
       </c>
       <c r="C5" t="n">
-        <v>683861.439999999</v>
+        <v>651126.8499999996</v>
       </c>
       <c r="D5" t="n">
-        <v>512271.8200000004</v>
+        <v>494595.4500000001</v>
       </c>
       <c r="E5" t="n">
-        <v>171589.62</v>
+        <v>156531.3999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>449865.2500000001</v>
+        <v>444253.6</v>
       </c>
       <c r="G5" t="n">
-        <v>233996.1899999998</v>
+        <v>206873.2499999999</v>
       </c>
       <c r="H5" t="n">
-        <v>15780.09</v>
+        <v>15729.09</v>
       </c>
       <c r="I5" t="n">
-        <v>1311046.590000001</v>
+        <v>1294158.07</v>
       </c>
     </row>
     <row r="6">
@@ -601,28 +601,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1945284.920000001</v>
+        <v>2099265.880000001</v>
       </c>
       <c r="C6" t="n">
-        <v>651126.8499999996</v>
+        <v>718976.5200000013</v>
       </c>
       <c r="D6" t="n">
-        <v>494595.4499999998</v>
+        <v>571683.3400000007</v>
       </c>
       <c r="E6" t="n">
-        <v>156531.3999999999</v>
+        <v>147293.1799999999</v>
       </c>
       <c r="F6" t="n">
-        <v>444253.6</v>
+        <v>430552.1299999998</v>
       </c>
       <c r="G6" t="n">
-        <v>206873.2500000001</v>
+        <v>288424.3899999998</v>
       </c>
       <c r="H6" t="n">
-        <v>15729.09</v>
+        <v>15687.89</v>
       </c>
       <c r="I6" t="n">
-        <v>1294158.070000001</v>
+        <v>1380289.36</v>
       </c>
     </row>
     <row r="7">
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2099265.880000003</v>
+        <v>2106777.06</v>
       </c>
       <c r="C7" t="n">
-        <v>718976.5200000012</v>
+        <v>716094.27</v>
       </c>
       <c r="D7" t="n">
-        <v>571683.3400000003</v>
+        <v>563071.9399999999</v>
       </c>
       <c r="E7" t="n">
-        <v>147293.1799999999</v>
+        <v>153022.3299999999</v>
       </c>
       <c r="F7" t="n">
-        <v>430552.13</v>
+        <v>423518.2899999999</v>
       </c>
       <c r="G7" t="n">
-        <v>288424.3900000002</v>
+        <v>292575.9800000005</v>
       </c>
       <c r="H7" t="n">
-        <v>15687.89</v>
+        <v>15550.55</v>
       </c>
       <c r="I7" t="n">
-        <v>1380289.360000001</v>
+        <v>1390682.79</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2106777.06</v>
+        <v>2106667.549999999</v>
       </c>
       <c r="C8" t="n">
-        <v>716094.2700000006</v>
+        <v>732744.2499999995</v>
       </c>
       <c r="D8" t="n">
-        <v>563071.9399999996</v>
+        <v>570709.6199999988</v>
       </c>
       <c r="E8" t="n">
-        <v>153022.3299999999</v>
+        <v>162034.6300000001</v>
       </c>
       <c r="F8" t="n">
-        <v>423518.29</v>
+        <v>428267.16</v>
       </c>
       <c r="G8" t="n">
-        <v>292575.98</v>
+        <v>304477.0899999998</v>
       </c>
       <c r="H8" t="n">
-        <v>15550.55</v>
+        <v>15638.16</v>
       </c>
       <c r="I8" t="n">
-        <v>1390682.789999999</v>
+        <v>1373923.299999999</v>
       </c>
     </row>
     <row r="9">
@@ -694,28 +694,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2106667.55</v>
+        <v>2167625.059999998</v>
       </c>
       <c r="C9" t="n">
-        <v>732744.2500000002</v>
+        <v>737997.3099999998</v>
       </c>
       <c r="D9" t="n">
-        <v>570709.6199999992</v>
+        <v>575797.9999999997</v>
       </c>
       <c r="E9" t="n">
-        <v>162034.6300000001</v>
+        <v>162199.31</v>
       </c>
       <c r="F9" t="n">
-        <v>428267.16</v>
+        <v>435654.08</v>
       </c>
       <c r="G9" t="n">
-        <v>304477.0899999996</v>
+        <v>302343.2300000001</v>
       </c>
       <c r="H9" t="n">
-        <v>15638.16</v>
+        <v>15461.44</v>
       </c>
       <c r="I9" t="n">
-        <v>1373923.3</v>
+        <v>1429627.749999998</v>
       </c>
     </row>
   </sheetData>

--- a/缓存数据/concat_area_csm_xm.xlsx
+++ b/缓存数据/concat_area_csm_xm.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2034261.629999999</v>
+        <v>2109747.670000001</v>
       </c>
       <c r="C2" t="n">
-        <v>729884.9899999998</v>
+        <v>1011974.570000001</v>
       </c>
       <c r="D2" t="n">
-        <v>577543.75</v>
+        <v>820433.5200000009</v>
       </c>
       <c r="E2" t="n">
-        <v>152341.24</v>
+        <v>191541.05</v>
       </c>
       <c r="F2" t="n">
-        <v>439059.9699999999</v>
+        <v>442741.0599999998</v>
       </c>
       <c r="G2" t="n">
-        <v>290825.02</v>
+        <v>569233.5100000002</v>
       </c>
       <c r="H2" t="n">
-        <v>16151.93</v>
+        <v>120440.95</v>
       </c>
       <c r="I2" t="n">
-        <v>1304376.639999999</v>
+        <v>1097773.1</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2022394.340000002</v>
+        <v>2286796.250000001</v>
       </c>
       <c r="C3" t="n">
-        <v>728751.3399999997</v>
+        <v>1214351.919999999</v>
       </c>
       <c r="D3" t="n">
-        <v>563337.62</v>
+        <v>1048553.789999998</v>
       </c>
       <c r="E3" t="n">
-        <v>165413.7200000001</v>
+        <v>165798.1299999999</v>
       </c>
       <c r="F3" t="n">
-        <v>445433.47</v>
+        <v>421982.6800000001</v>
       </c>
       <c r="G3" t="n">
-        <v>283317.8699999998</v>
+        <v>792369.2399999984</v>
       </c>
       <c r="H3" t="n">
-        <v>16225.19</v>
+        <v>421991.3900000001</v>
       </c>
       <c r="I3" t="n">
-        <v>1293643.000000002</v>
+        <v>1072444.330000001</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1994908.029999998</v>
+        <v>2141243.08</v>
       </c>
       <c r="C4" t="n">
-        <v>683861.439999999</v>
+        <v>1165071.549999999</v>
       </c>
       <c r="D4" t="n">
-        <v>512271.8200000006</v>
+        <v>1024383.22</v>
       </c>
       <c r="E4" t="n">
-        <v>171589.62</v>
+        <v>140688.33</v>
       </c>
       <c r="F4" t="n">
-        <v>449865.2500000002</v>
+        <v>397917.35</v>
       </c>
       <c r="G4" t="n">
-        <v>233996.1899999999</v>
+        <v>767154.1999999995</v>
       </c>
       <c r="H4" t="n">
-        <v>15780.09</v>
+        <v>421241.77</v>
       </c>
       <c r="I4" t="n">
-        <v>1311046.589999999</v>
+        <v>976171.5300000007</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1945284.92</v>
+        <v>2105176.280000001</v>
       </c>
       <c r="C5" t="n">
-        <v>651126.8499999996</v>
+        <v>1093367.49</v>
       </c>
       <c r="D5" t="n">
-        <v>494595.4500000001</v>
+        <v>916227.8800000005</v>
       </c>
       <c r="E5" t="n">
-        <v>156531.3999999999</v>
+        <v>177139.61</v>
       </c>
       <c r="F5" t="n">
-        <v>444253.6</v>
+        <v>432548.17</v>
       </c>
       <c r="G5" t="n">
-        <v>206873.2499999999</v>
+        <v>660819.3199999996</v>
       </c>
       <c r="H5" t="n">
-        <v>15729.09</v>
+        <v>420991.73</v>
       </c>
       <c r="I5" t="n">
-        <v>1294158.07</v>
+        <v>1011808.790000001</v>
       </c>
     </row>
     <row r="6">
@@ -601,28 +601,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2099265.880000001</v>
+        <v>2228677.359999999</v>
       </c>
       <c r="C6" t="n">
-        <v>718976.5200000013</v>
+        <v>1105451.049999999</v>
       </c>
       <c r="D6" t="n">
-        <v>571683.3400000007</v>
+        <v>879722.4499999993</v>
       </c>
       <c r="E6" t="n">
-        <v>147293.1799999999</v>
+        <v>225728.6000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>430552.1299999998</v>
+        <v>494124.3700000001</v>
       </c>
       <c r="G6" t="n">
-        <v>288424.3899999998</v>
+        <v>611326.6799999996</v>
       </c>
       <c r="H6" t="n">
-        <v>15687.89</v>
+        <v>420813.16</v>
       </c>
       <c r="I6" t="n">
-        <v>1380289.36</v>
+        <v>1123226.310000001</v>
       </c>
     </row>
     <row r="7">
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2106777.06</v>
+        <v>1958253.23</v>
       </c>
       <c r="C7" t="n">
-        <v>716094.27</v>
+        <v>729113.2199999996</v>
       </c>
       <c r="D7" t="n">
-        <v>563071.9399999999</v>
+        <v>551613.0100000001</v>
       </c>
       <c r="E7" t="n">
-        <v>153022.3299999999</v>
+        <v>177500.21</v>
       </c>
       <c r="F7" t="n">
-        <v>423518.2899999999</v>
+        <v>442646.4299999999</v>
       </c>
       <c r="G7" t="n">
-        <v>292575.9800000005</v>
+        <v>286466.7899999998</v>
       </c>
       <c r="H7" t="n">
-        <v>15550.55</v>
+        <v>21821.82</v>
       </c>
       <c r="I7" t="n">
-        <v>1390682.79</v>
+        <v>1229140.010000001</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2106667.549999999</v>
+        <v>1845496</v>
       </c>
       <c r="C8" t="n">
-        <v>732744.2499999995</v>
+        <v>721499.1600000004</v>
       </c>
       <c r="D8" t="n">
-        <v>570709.6199999988</v>
+        <v>545710.7600000002</v>
       </c>
       <c r="E8" t="n">
-        <v>162034.6300000001</v>
+        <v>175788.4000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>428267.16</v>
+        <v>422912.1599999999</v>
       </c>
       <c r="G8" t="n">
-        <v>304477.0899999998</v>
+        <v>298587.0000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>15638.16</v>
+        <v>21748.88</v>
       </c>
       <c r="I8" t="n">
-        <v>1373923.299999999</v>
+        <v>1123996.84</v>
       </c>
     </row>
     <row r="9">
@@ -694,31 +694,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2167625.059999998</v>
+        <v>1646420.979999999</v>
       </c>
       <c r="C9" t="n">
-        <v>737997.3099999998</v>
+        <v>697766.4899999994</v>
       </c>
       <c r="D9" t="n">
-        <v>575797.9999999997</v>
+        <v>552832.1600000004</v>
       </c>
       <c r="E9" t="n">
-        <v>162199.31</v>
+        <v>144934.3299999999</v>
       </c>
       <c r="F9" t="n">
-        <v>435654.08</v>
+        <v>399217.5799999999</v>
       </c>
       <c r="G9" t="n">
-        <v>302343.2300000001</v>
+        <v>298548.91</v>
       </c>
       <c r="H9" t="n">
-        <v>15461.44</v>
+        <v>21877.96</v>
       </c>
       <c r="I9" t="n">
-        <v>1429627.749999998</v>
+        <v>948654.4899999995</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>